--- a/DataTables/DetailText/剧情/000_06金钱过低.xlsx
+++ b/DataTables/DetailText/剧情/000_06金钱过低.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73017DE-437C-48A1-93B0-626108B4958D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9641758B-61F8-48B5-A08C-1E6727F78917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -165,9 +165,6 @@
   </si>
   <si>
     <t>≤</t>
-  </si>
-  <si>
-    <t>end_game</t>
   </si>
   <si>
     <t>night</t>
@@ -237,6 +234,9 @@
   <si>
     <t>000_06</t>
     <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>endgame</t>
   </si>
 </sst>
 </file>
@@ -768,13 +768,13 @@
     </row>
     <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
       <c r="A2" s="29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" s="25" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" s="23"/>
       <c r="E2" s="23" t="s">
@@ -789,7 +789,7 @@
       <c r="J2" s="22"/>
       <c r="K2" s="23"/>
       <c r="L2" s="23" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="M2" s="22"/>
       <c r="N2" s="23"/>
@@ -1024,7 +1024,7 @@
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="L2" xr:uid="{CB93CAC9-E05A-42CD-BF51-C2A084B5D84B}">
-      <formula1>"clinic,night,end_game"</formula1>
+      <formula1>"clinic,night,endgame"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="E2 G2" xr:uid="{EEAB203E-6BC2-440A-AE17-A1B685A828E0}">
       <formula1>"≥,≤"</formula1>
@@ -1087,10 +1087,10 @@
         <v>9</v>
       </c>
       <c r="C2" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="27" t="s">
         <v>35</v>
-      </c>
-      <c r="D2" s="27" t="s">
-        <v>36</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="7"/>
@@ -1098,7 +1098,7 @@
         <v>10</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1113,10 +1113,10 @@
       <c r="E3" s="2"/>
       <c r="F3" s="7"/>
       <c r="G3" s="30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H3" s="26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:8">

--- a/DataTables/DetailText/剧情/000_06金钱过低.xlsx
+++ b/DataTables/DetailText/剧情/000_06金钱过低.xlsx
@@ -1,35 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9641758B-61F8-48B5-A08C-1E6727F78917}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7436E81A-3F66-4CA0-9A68-D4CD9417F48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="4035" windowWidth="12060" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -236,7 +223,7 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>endgame</t>
+    <t>gameover</t>
   </si>
 </sst>
 </file>
@@ -475,7 +462,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -686,7 +673,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.625" customWidth="1"/>
@@ -704,7 +691,7 @@
     <col min="19" max="20" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="21" customFormat="1">
       <c r="A1" s="16" t="s">
         <v>13</v>
       </c>
@@ -766,7 +753,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="21" customFormat="1">
       <c r="A2" s="29" t="s">
         <v>39</v>
       </c>
@@ -1023,14 +1010,14 @@
     <dataValidation type="list" sqref="S2:S10" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="L2" xr:uid="{CB93CAC9-E05A-42CD-BF51-C2A084B5D84B}">
-      <formula1>"clinic,night,endgame"</formula1>
-    </dataValidation>
     <dataValidation type="list" sqref="E2 G2" xr:uid="{EEAB203E-6BC2-440A-AE17-A1B685A828E0}">
       <formula1>"≥,≤"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="C2" xr:uid="{6ECE54C8-5545-4B8F-B19D-F059532E0477}">
       <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{44B4CE45-334B-44D9-BC89-C70DCE5D0121}">
+      <formula1>"clinic,night,gameover,endgame"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DataTables/DetailText/剧情/000_06金钱过低.xlsx
+++ b/DataTables/DetailText/剧情/000_06金钱过低.xlsx
@@ -1,27 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7436E81A-3F66-4CA0-9A68-D4CD9417F48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555CEF26-3717-4EC5-A6D4-182BE0631B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="4035" windowWidth="12060" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3435" yWindow="6495" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>LineIndex</t>
   </si>
@@ -224,6 +237,10 @@
   </si>
   <si>
     <t>gameover</t>
+  </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
@@ -370,7 +387,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -460,9 +477,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -673,7 +696,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.625" customWidth="1"/>
@@ -691,7 +714,7 @@
     <col min="19" max="20" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="21" customFormat="1">
+    <row r="1" spans="1:20" s="21" customFormat="1" ht="18">
       <c r="A1" s="16" t="s">
         <v>13</v>
       </c>
@@ -753,7 +776,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="21" customFormat="1">
+    <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
       <c r="A2" s="29" t="s">
         <v>39</v>
       </c>
@@ -1026,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" customWidth="1"/>
@@ -1040,7 +1063,7 @@
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1065,8 +1088,11 @@
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1087,8 +1113,9 @@
       <c r="H2" s="26" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="28"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1105,8 +1132,9 @@
       <c r="H3" s="26" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="28"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1115,8 +1143,9 @@
       <c r="F4" s="7"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="28"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1125,8 +1154,9 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="28"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1135,8 +1165,9 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="28"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1145,6 +1176,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
+      <c r="I7" s="32"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4"/>

--- a/DataTables/DetailText/剧情/000_06金钱过低.xlsx
+++ b/DataTables/DetailText/剧情/000_06金钱过低.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555CEF26-3717-4EC5-A6D4-182BE0631B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0284769-0934-43B1-A219-CF24ACBD3218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3435" yWindow="6495" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -179,10 +179,6 @@
   </si>
   <si>
     <t>因经营不善，医馆被迫关闭</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>东璧锕，咱们这医馆已经经营不下去了，我们收拾行李回乡下老家吧…</t>
     <phoneticPr fontId="4"/>
   </si>
   <si>
@@ -240,6 +236,10 @@
   </si>
   <si>
     <t>Music</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>东璧啊，咱们这医馆已经经营不下去了，我们收拾行李回乡下老家吧…</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -778,7 +778,7 @@
     </row>
     <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
       <c r="A2" s="29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" s="25" t="s">
         <v>31</v>
@@ -799,7 +799,7 @@
       <c r="J2" s="22"/>
       <c r="K2" s="23"/>
       <c r="L2" s="23" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M2" s="22"/>
       <c r="N2" s="23"/>
@@ -1089,7 +1089,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1111,7 +1111,7 @@
         <v>10</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I2" s="28"/>
     </row>
@@ -1127,7 +1127,7 @@
       <c r="E3" s="2"/>
       <c r="F3" s="7"/>
       <c r="G3" s="30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H3" s="26" t="s">
         <v>36</v>
